--- a/최종산출물/2. WBS/[1조] WBS_현대이지웰_최종프로젝트 (1).xlsx
+++ b/최종산출물/2. WBS/[1조] WBS_현대이지웰_최종프로젝트 (1).xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="328" documentId="11_9E7544CE3A9CF0EF1C211E032755EE978402C9E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2426AC41-8503-459A-B89E-FCE91CA882C6}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lsh/Documents/GitHub/Projects/Web/ticketingMaster_doc/최종산출물/2. WBS/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D7B62A-F16E-F44F-9838-24A2D12F7C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34120" yWindow="200" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ticketing-master" sheetId="1" r:id="rId1"/>
@@ -307,7 +312,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1257,9 +1262,60 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1287,15 +1343,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1305,62 +1363,9 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1661,411 +1666,411 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BV44"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="13" customWidth="1"/>
     <col min="2" max="2" width="11" style="13" customWidth="1"/>
-    <col min="3" max="3" width="47.42578125" style="13" customWidth="1"/>
+    <col min="3" max="3" width="47.5" style="13" customWidth="1"/>
     <col min="4" max="4" width="11" style="13" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" style="56" customWidth="1"/>
-    <col min="6" max="6" width="1.5703125" style="1" customWidth="1"/>
-    <col min="7" max="68" width="1.5703125" style="2" customWidth="1"/>
-    <col min="69" max="69" width="9.140625" style="2" customWidth="1"/>
-    <col min="70" max="16384" width="9.140625" style="2"/>
+    <col min="5" max="5" width="11.33203125" style="56" customWidth="1"/>
+    <col min="6" max="6" width="1.5" style="1" customWidth="1"/>
+    <col min="7" max="68" width="1.5" style="2" customWidth="1"/>
+    <col min="69" max="69" width="9.1640625" style="2" customWidth="1"/>
+    <col min="70" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:74" ht="15" customHeight="1">
-      <c r="A1" s="74" t="s">
+    <row r="1" spans="1:74" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75"/>
-      <c r="V1" s="75"/>
-      <c r="W1" s="75"/>
-      <c r="X1" s="75"/>
-      <c r="Y1" s="75"/>
-      <c r="Z1" s="75"/>
-      <c r="AA1" s="75"/>
-      <c r="AB1" s="75"/>
-      <c r="AC1" s="75"/>
-      <c r="AD1" s="75"/>
-      <c r="AE1" s="75"/>
-      <c r="AF1" s="75"/>
-      <c r="AG1" s="75"/>
-      <c r="AH1" s="75"/>
-      <c r="AI1" s="75"/>
-      <c r="AJ1" s="75"/>
-      <c r="AK1" s="75"/>
-      <c r="AL1" s="75"/>
-      <c r="AM1" s="75"/>
-      <c r="AN1" s="75"/>
-      <c r="AO1" s="75"/>
-      <c r="AP1" s="75"/>
-      <c r="AQ1" s="75"/>
-      <c r="AR1" s="75"/>
-      <c r="AS1" s="75"/>
-      <c r="AT1" s="75"/>
-      <c r="AU1" s="75"/>
-      <c r="AV1" s="75"/>
-      <c r="AW1" s="75"/>
-      <c r="AX1" s="75"/>
-      <c r="AY1" s="75"/>
-      <c r="AZ1" s="75"/>
-      <c r="BA1" s="75"/>
-      <c r="BB1" s="75"/>
-      <c r="BC1" s="75"/>
-      <c r="BD1" s="75"/>
-      <c r="BE1" s="75"/>
-      <c r="BF1" s="75"/>
-      <c r="BG1" s="75"/>
-      <c r="BH1" s="75"/>
-      <c r="BI1" s="75"/>
-      <c r="BJ1" s="75"/>
-      <c r="BK1" s="75"/>
-      <c r="BL1" s="75"/>
-      <c r="BM1" s="75"/>
-      <c r="BN1" s="75"/>
-      <c r="BO1" s="75"/>
-      <c r="BP1" s="76"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
+      <c r="N1" s="94"/>
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="94"/>
+      <c r="R1" s="94"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="94"/>
+      <c r="V1" s="94"/>
+      <c r="W1" s="94"/>
+      <c r="X1" s="94"/>
+      <c r="Y1" s="94"/>
+      <c r="Z1" s="94"/>
+      <c r="AA1" s="94"/>
+      <c r="AB1" s="94"/>
+      <c r="AC1" s="94"/>
+      <c r="AD1" s="94"/>
+      <c r="AE1" s="94"/>
+      <c r="AF1" s="94"/>
+      <c r="AG1" s="94"/>
+      <c r="AH1" s="94"/>
+      <c r="AI1" s="94"/>
+      <c r="AJ1" s="94"/>
+      <c r="AK1" s="94"/>
+      <c r="AL1" s="94"/>
+      <c r="AM1" s="94"/>
+      <c r="AN1" s="94"/>
+      <c r="AO1" s="94"/>
+      <c r="AP1" s="94"/>
+      <c r="AQ1" s="94"/>
+      <c r="AR1" s="94"/>
+      <c r="AS1" s="94"/>
+      <c r="AT1" s="94"/>
+      <c r="AU1" s="94"/>
+      <c r="AV1" s="94"/>
+      <c r="AW1" s="94"/>
+      <c r="AX1" s="94"/>
+      <c r="AY1" s="94"/>
+      <c r="AZ1" s="94"/>
+      <c r="BA1" s="94"/>
+      <c r="BB1" s="94"/>
+      <c r="BC1" s="94"/>
+      <c r="BD1" s="94"/>
+      <c r="BE1" s="94"/>
+      <c r="BF1" s="94"/>
+      <c r="BG1" s="94"/>
+      <c r="BH1" s="94"/>
+      <c r="BI1" s="94"/>
+      <c r="BJ1" s="94"/>
+      <c r="BK1" s="94"/>
+      <c r="BL1" s="94"/>
+      <c r="BM1" s="94"/>
+      <c r="BN1" s="94"/>
+      <c r="BO1" s="94"/>
+      <c r="BP1" s="95"/>
       <c r="BQ1" s="1"/>
     </row>
-    <row r="2" spans="1:74" ht="15" customHeight="1">
-      <c r="A2" s="77"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="78"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="78"/>
-      <c r="U2" s="78"/>
-      <c r="V2" s="78"/>
-      <c r="W2" s="78"/>
-      <c r="X2" s="78"/>
-      <c r="Y2" s="78"/>
-      <c r="Z2" s="78"/>
-      <c r="AA2" s="78"/>
-      <c r="AB2" s="78"/>
-      <c r="AC2" s="78"/>
-      <c r="AD2" s="78"/>
-      <c r="AE2" s="78"/>
-      <c r="AF2" s="78"/>
-      <c r="AG2" s="78"/>
-      <c r="AH2" s="78"/>
-      <c r="AI2" s="78"/>
-      <c r="AJ2" s="78"/>
-      <c r="AK2" s="78"/>
-      <c r="AL2" s="78"/>
-      <c r="AM2" s="78"/>
-      <c r="AN2" s="78"/>
-      <c r="AO2" s="78"/>
-      <c r="AP2" s="78"/>
-      <c r="AQ2" s="78"/>
-      <c r="AR2" s="78"/>
-      <c r="AS2" s="78"/>
-      <c r="AT2" s="78"/>
-      <c r="AU2" s="78"/>
-      <c r="AV2" s="78"/>
-      <c r="AW2" s="78"/>
-      <c r="AX2" s="78"/>
-      <c r="AY2" s="78"/>
-      <c r="AZ2" s="78"/>
-      <c r="BA2" s="78"/>
-      <c r="BB2" s="78"/>
-      <c r="BC2" s="78"/>
-      <c r="BD2" s="78"/>
-      <c r="BE2" s="78"/>
-      <c r="BF2" s="78"/>
-      <c r="BG2" s="78"/>
-      <c r="BH2" s="78"/>
-      <c r="BI2" s="78"/>
-      <c r="BJ2" s="78"/>
-      <c r="BK2" s="78"/>
-      <c r="BL2" s="78"/>
-      <c r="BM2" s="78"/>
-      <c r="BN2" s="78"/>
-      <c r="BO2" s="78"/>
-      <c r="BP2" s="79"/>
+    <row r="2" spans="1:74" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="96"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
+      <c r="M2" s="97"/>
+      <c r="N2" s="97"/>
+      <c r="O2" s="97"/>
+      <c r="P2" s="97"/>
+      <c r="Q2" s="97"/>
+      <c r="R2" s="97"/>
+      <c r="S2" s="97"/>
+      <c r="T2" s="97"/>
+      <c r="U2" s="97"/>
+      <c r="V2" s="97"/>
+      <c r="W2" s="97"/>
+      <c r="X2" s="97"/>
+      <c r="Y2" s="97"/>
+      <c r="Z2" s="97"/>
+      <c r="AA2" s="97"/>
+      <c r="AB2" s="97"/>
+      <c r="AC2" s="97"/>
+      <c r="AD2" s="97"/>
+      <c r="AE2" s="97"/>
+      <c r="AF2" s="97"/>
+      <c r="AG2" s="97"/>
+      <c r="AH2" s="97"/>
+      <c r="AI2" s="97"/>
+      <c r="AJ2" s="97"/>
+      <c r="AK2" s="97"/>
+      <c r="AL2" s="97"/>
+      <c r="AM2" s="97"/>
+      <c r="AN2" s="97"/>
+      <c r="AO2" s="97"/>
+      <c r="AP2" s="97"/>
+      <c r="AQ2" s="97"/>
+      <c r="AR2" s="97"/>
+      <c r="AS2" s="97"/>
+      <c r="AT2" s="97"/>
+      <c r="AU2" s="97"/>
+      <c r="AV2" s="97"/>
+      <c r="AW2" s="97"/>
+      <c r="AX2" s="97"/>
+      <c r="AY2" s="97"/>
+      <c r="AZ2" s="97"/>
+      <c r="BA2" s="97"/>
+      <c r="BB2" s="97"/>
+      <c r="BC2" s="97"/>
+      <c r="BD2" s="97"/>
+      <c r="BE2" s="97"/>
+      <c r="BF2" s="97"/>
+      <c r="BG2" s="97"/>
+      <c r="BH2" s="97"/>
+      <c r="BI2" s="97"/>
+      <c r="BJ2" s="97"/>
+      <c r="BK2" s="97"/>
+      <c r="BL2" s="97"/>
+      <c r="BM2" s="97"/>
+      <c r="BN2" s="97"/>
+      <c r="BO2" s="97"/>
+      <c r="BP2" s="98"/>
       <c r="BQ2" s="1"/>
     </row>
-    <row r="3" spans="1:74" ht="15" customHeight="1">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
-      <c r="O3" s="81"/>
-      <c r="P3" s="81"/>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="81"/>
-      <c r="S3" s="81"/>
-      <c r="T3" s="81"/>
-      <c r="U3" s="81"/>
-      <c r="V3" s="81"/>
-      <c r="W3" s="81"/>
-      <c r="X3" s="81"/>
-      <c r="Y3" s="81"/>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
-      <c r="AB3" s="81"/>
-      <c r="AC3" s="81"/>
-      <c r="AD3" s="81"/>
-      <c r="AE3" s="81"/>
-      <c r="AF3" s="81"/>
-      <c r="AG3" s="81"/>
-      <c r="AH3" s="81"/>
-      <c r="AI3" s="81"/>
-      <c r="AJ3" s="81"/>
-      <c r="AK3" s="81"/>
-      <c r="AL3" s="81"/>
-      <c r="AM3" s="81"/>
-      <c r="AN3" s="81"/>
-      <c r="AO3" s="81"/>
-      <c r="AP3" s="81"/>
-      <c r="AQ3" s="81"/>
-      <c r="AR3" s="81"/>
-      <c r="AS3" s="81"/>
-      <c r="AT3" s="81"/>
-      <c r="AU3" s="81"/>
-      <c r="AV3" s="81"/>
-      <c r="AW3" s="81"/>
-      <c r="AX3" s="81"/>
-      <c r="AY3" s="81"/>
-      <c r="AZ3" s="81"/>
-      <c r="BA3" s="81"/>
-      <c r="BB3" s="81"/>
-      <c r="BC3" s="81"/>
-      <c r="BD3" s="81"/>
-      <c r="BE3" s="81"/>
-      <c r="BF3" s="81"/>
-      <c r="BG3" s="81"/>
-      <c r="BH3" s="81"/>
-      <c r="BI3" s="81"/>
-      <c r="BJ3" s="81"/>
-      <c r="BK3" s="81"/>
-      <c r="BL3" s="81"/>
-      <c r="BM3" s="81"/>
-      <c r="BN3" s="81"/>
-      <c r="BO3" s="81"/>
-      <c r="BP3" s="82"/>
+    <row r="3" spans="1:74" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="99"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="100"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="100"/>
+      <c r="N3" s="100"/>
+      <c r="O3" s="100"/>
+      <c r="P3" s="100"/>
+      <c r="Q3" s="100"/>
+      <c r="R3" s="100"/>
+      <c r="S3" s="100"/>
+      <c r="T3" s="100"/>
+      <c r="U3" s="100"/>
+      <c r="V3" s="100"/>
+      <c r="W3" s="100"/>
+      <c r="X3" s="100"/>
+      <c r="Y3" s="100"/>
+      <c r="Z3" s="100"/>
+      <c r="AA3" s="100"/>
+      <c r="AB3" s="100"/>
+      <c r="AC3" s="100"/>
+      <c r="AD3" s="100"/>
+      <c r="AE3" s="100"/>
+      <c r="AF3" s="100"/>
+      <c r="AG3" s="100"/>
+      <c r="AH3" s="100"/>
+      <c r="AI3" s="100"/>
+      <c r="AJ3" s="100"/>
+      <c r="AK3" s="100"/>
+      <c r="AL3" s="100"/>
+      <c r="AM3" s="100"/>
+      <c r="AN3" s="100"/>
+      <c r="AO3" s="100"/>
+      <c r="AP3" s="100"/>
+      <c r="AQ3" s="100"/>
+      <c r="AR3" s="100"/>
+      <c r="AS3" s="100"/>
+      <c r="AT3" s="100"/>
+      <c r="AU3" s="100"/>
+      <c r="AV3" s="100"/>
+      <c r="AW3" s="100"/>
+      <c r="AX3" s="100"/>
+      <c r="AY3" s="100"/>
+      <c r="AZ3" s="100"/>
+      <c r="BA3" s="100"/>
+      <c r="BB3" s="100"/>
+      <c r="BC3" s="100"/>
+      <c r="BD3" s="100"/>
+      <c r="BE3" s="100"/>
+      <c r="BF3" s="100"/>
+      <c r="BG3" s="100"/>
+      <c r="BH3" s="100"/>
+      <c r="BI3" s="100"/>
+      <c r="BJ3" s="100"/>
+      <c r="BK3" s="100"/>
+      <c r="BL3" s="100"/>
+      <c r="BM3" s="100"/>
+      <c r="BN3" s="100"/>
+      <c r="BO3" s="100"/>
+      <c r="BP3" s="101"/>
       <c r="BQ3" s="1"/>
     </row>
-    <row r="4" spans="1:74" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="84" t="s">
+    <row r="4" spans="1:74" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="91" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="83" t="s">
+      <c r="C4" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="83" t="s">
+      <c r="D4" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="85" t="s">
+      <c r="E4" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="85" t="s">
+      <c r="F4" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="104"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="104"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="104"/>
-      <c r="L4" s="105"/>
-      <c r="M4" s="86" t="s">
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="107"/>
+      <c r="L4" s="108"/>
+      <c r="M4" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="87"/>
-      <c r="O4" s="87"/>
-      <c r="P4" s="87"/>
-      <c r="Q4" s="87"/>
-      <c r="R4" s="87"/>
-      <c r="S4" s="87"/>
-      <c r="T4" s="87"/>
-      <c r="U4" s="87"/>
-      <c r="V4" s="87"/>
-      <c r="W4" s="87"/>
-      <c r="X4" s="87"/>
-      <c r="Y4" s="87"/>
-      <c r="Z4" s="87"/>
-      <c r="AA4" s="87"/>
-      <c r="AB4" s="87"/>
-      <c r="AC4" s="87"/>
-      <c r="AD4" s="87"/>
-      <c r="AE4" s="87"/>
-      <c r="AF4" s="87"/>
-      <c r="AG4" s="87"/>
-      <c r="AH4" s="87"/>
-      <c r="AI4" s="87"/>
-      <c r="AJ4" s="87"/>
-      <c r="AK4" s="87"/>
-      <c r="AL4" s="87"/>
-      <c r="AM4" s="87"/>
-      <c r="AN4" s="87"/>
-      <c r="AO4" s="86" t="s">
+      <c r="N4" s="110"/>
+      <c r="O4" s="110"/>
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110"/>
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110"/>
+      <c r="V4" s="110"/>
+      <c r="W4" s="110"/>
+      <c r="X4" s="110"/>
+      <c r="Y4" s="110"/>
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="110"/>
+      <c r="AE4" s="110"/>
+      <c r="AF4" s="110"/>
+      <c r="AG4" s="110"/>
+      <c r="AH4" s="110"/>
+      <c r="AI4" s="110"/>
+      <c r="AJ4" s="110"/>
+      <c r="AK4" s="110"/>
+      <c r="AL4" s="110"/>
+      <c r="AM4" s="110"/>
+      <c r="AN4" s="110"/>
+      <c r="AO4" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="AP4" s="87"/>
-      <c r="AQ4" s="87"/>
-      <c r="AR4" s="87"/>
-      <c r="AS4" s="87"/>
-      <c r="AT4" s="87"/>
-      <c r="AU4" s="87"/>
-      <c r="AV4" s="87"/>
-      <c r="AW4" s="87"/>
-      <c r="AX4" s="87"/>
-      <c r="AY4" s="87"/>
-      <c r="AZ4" s="87"/>
-      <c r="BA4" s="87"/>
-      <c r="BB4" s="87"/>
-      <c r="BC4" s="87"/>
-      <c r="BD4" s="87"/>
-      <c r="BE4" s="87"/>
-      <c r="BF4" s="87"/>
-      <c r="BG4" s="87"/>
-      <c r="BH4" s="87"/>
-      <c r="BI4" s="87"/>
-      <c r="BJ4" s="87"/>
-      <c r="BK4" s="87"/>
-      <c r="BL4" s="87"/>
-      <c r="BM4" s="87"/>
-      <c r="BN4" s="87"/>
-      <c r="BO4" s="87"/>
-      <c r="BP4" s="88"/>
+      <c r="AP4" s="110"/>
+      <c r="AQ4" s="110"/>
+      <c r="AR4" s="110"/>
+      <c r="AS4" s="110"/>
+      <c r="AT4" s="110"/>
+      <c r="AU4" s="110"/>
+      <c r="AV4" s="110"/>
+      <c r="AW4" s="110"/>
+      <c r="AX4" s="110"/>
+      <c r="AY4" s="110"/>
+      <c r="AZ4" s="110"/>
+      <c r="BA4" s="110"/>
+      <c r="BB4" s="110"/>
+      <c r="BC4" s="110"/>
+      <c r="BD4" s="110"/>
+      <c r="BE4" s="110"/>
+      <c r="BF4" s="110"/>
+      <c r="BG4" s="110"/>
+      <c r="BH4" s="110"/>
+      <c r="BI4" s="110"/>
+      <c r="BJ4" s="110"/>
+      <c r="BK4" s="110"/>
+      <c r="BL4" s="110"/>
+      <c r="BM4" s="110"/>
+      <c r="BN4" s="110"/>
+      <c r="BO4" s="110"/>
+      <c r="BP4" s="111"/>
       <c r="BQ4" s="1"/>
     </row>
-    <row r="5" spans="1:74" ht="30" customHeight="1">
-      <c r="A5" s="106"/>
-      <c r="B5" s="107"/>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="73" t="s">
+    <row r="5" spans="1:74" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="104"/>
+      <c r="B5" s="92"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="109"/>
-      <c r="H5" s="109"/>
-      <c r="I5" s="109"/>
-      <c r="J5" s="109"/>
-      <c r="K5" s="109"/>
-      <c r="L5" s="110"/>
-      <c r="M5" s="73" t="s">
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
+      <c r="K5" s="89"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="109"/>
-      <c r="O5" s="109"/>
-      <c r="P5" s="109"/>
-      <c r="Q5" s="109"/>
-      <c r="R5" s="109"/>
-      <c r="S5" s="110"/>
-      <c r="T5" s="73" t="s">
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="U5" s="109"/>
-      <c r="V5" s="109"/>
-      <c r="W5" s="109"/>
-      <c r="X5" s="109"/>
-      <c r="Y5" s="109"/>
-      <c r="Z5" s="110"/>
-      <c r="AA5" s="73" t="s">
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
+      <c r="W5" s="89"/>
+      <c r="X5" s="89"/>
+      <c r="Y5" s="89"/>
+      <c r="Z5" s="90"/>
+      <c r="AA5" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="AB5" s="109"/>
-      <c r="AC5" s="109"/>
-      <c r="AD5" s="109"/>
-      <c r="AE5" s="109"/>
-      <c r="AF5" s="109"/>
-      <c r="AG5" s="110"/>
-      <c r="AH5" s="73" t="s">
+      <c r="AB5" s="89"/>
+      <c r="AC5" s="89"/>
+      <c r="AD5" s="89"/>
+      <c r="AE5" s="89"/>
+      <c r="AF5" s="89"/>
+      <c r="AG5" s="90"/>
+      <c r="AH5" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="AI5" s="109"/>
-      <c r="AJ5" s="109"/>
-      <c r="AK5" s="109"/>
-      <c r="AL5" s="109"/>
-      <c r="AM5" s="109"/>
-      <c r="AN5" s="110"/>
-      <c r="AO5" s="73" t="s">
+      <c r="AI5" s="89"/>
+      <c r="AJ5" s="89"/>
+      <c r="AK5" s="89"/>
+      <c r="AL5" s="89"/>
+      <c r="AM5" s="89"/>
+      <c r="AN5" s="90"/>
+      <c r="AO5" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="AP5" s="109"/>
-      <c r="AQ5" s="109"/>
-      <c r="AR5" s="109"/>
-      <c r="AS5" s="109"/>
-      <c r="AT5" s="109"/>
-      <c r="AU5" s="110"/>
-      <c r="AV5" s="73" t="s">
+      <c r="AP5" s="89"/>
+      <c r="AQ5" s="89"/>
+      <c r="AR5" s="89"/>
+      <c r="AS5" s="89"/>
+      <c r="AT5" s="89"/>
+      <c r="AU5" s="90"/>
+      <c r="AV5" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="AW5" s="109"/>
-      <c r="AX5" s="109"/>
-      <c r="AY5" s="109"/>
-      <c r="AZ5" s="109"/>
-      <c r="BA5" s="109"/>
-      <c r="BB5" s="110"/>
-      <c r="BC5" s="73" t="s">
+      <c r="AW5" s="89"/>
+      <c r="AX5" s="89"/>
+      <c r="AY5" s="89"/>
+      <c r="AZ5" s="89"/>
+      <c r="BA5" s="89"/>
+      <c r="BB5" s="90"/>
+      <c r="BC5" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="BD5" s="109"/>
-      <c r="BE5" s="109"/>
-      <c r="BF5" s="109"/>
-      <c r="BG5" s="109"/>
-      <c r="BH5" s="109"/>
-      <c r="BI5" s="110"/>
-      <c r="BJ5" s="73" t="s">
+      <c r="BD5" s="89"/>
+      <c r="BE5" s="89"/>
+      <c r="BF5" s="89"/>
+      <c r="BG5" s="89"/>
+      <c r="BH5" s="89"/>
+      <c r="BI5" s="90"/>
+      <c r="BJ5" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="BK5" s="109"/>
-      <c r="BL5" s="109"/>
-      <c r="BM5" s="109"/>
-      <c r="BN5" s="109"/>
-      <c r="BO5" s="109"/>
-      <c r="BP5" s="111"/>
+      <c r="BK5" s="89"/>
+      <c r="BL5" s="89"/>
+      <c r="BM5" s="89"/>
+      <c r="BN5" s="89"/>
+      <c r="BO5" s="89"/>
+      <c r="BP5" s="102"/>
       <c r="BQ5" s="1"/>
     </row>
-    <row r="6" spans="1:74" ht="21.95" customHeight="1">
+    <row r="6" spans="1:74" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="20" t="s">
         <v>18</v>
       </c>
@@ -2081,8 +2086,8 @@
       <c r="E6" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="98"/>
-      <c r="G6" s="99"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="75"/>
       <c r="H6" s="18"/>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
@@ -2146,8 +2151,8 @@
       <c r="BP6" s="19"/>
       <c r="BQ6" s="1"/>
     </row>
-    <row r="7" spans="1:74" ht="21.95" customHeight="1">
-      <c r="A7" s="89" t="s">
+    <row r="7" spans="1:74" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="80" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="24" t="s">
@@ -2164,8 +2169,8 @@
       </c>
       <c r="F7" s="58"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="100"/>
-      <c r="I7" s="100"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -2227,8 +2232,8 @@
       <c r="BP7" s="5"/>
       <c r="BQ7" s="1"/>
     </row>
-    <row r="8" spans="1:74" ht="21.95" customHeight="1">
-      <c r="A8" s="90"/>
+    <row r="8" spans="1:74" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="81"/>
       <c r="B8" s="25" t="s">
         <v>26</v>
       </c>
@@ -2245,9 +2250,9 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
-      <c r="J8" s="101"/>
-      <c r="K8" s="101"/>
-      <c r="L8" s="101"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="77"/>
+      <c r="L8" s="77"/>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
@@ -2306,8 +2311,8 @@
       <c r="BP8" s="8"/>
       <c r="BQ8" s="1"/>
     </row>
-    <row r="9" spans="1:74" ht="21.95" customHeight="1">
-      <c r="A9" s="91" t="s">
+    <row r="9" spans="1:74" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="82" t="s">
         <v>28</v>
       </c>
       <c r="B9" s="24" t="s">
@@ -2387,8 +2392,8 @@
       <c r="BP9" s="5"/>
       <c r="BQ9" s="1"/>
     </row>
-    <row r="10" spans="1:74" ht="21.95" customHeight="1">
-      <c r="A10" s="91"/>
+    <row r="10" spans="1:74" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="82"/>
       <c r="B10" s="26" t="s">
         <v>29</v>
       </c>
@@ -2449,8 +2454,8 @@
       <c r="BP10" s="10"/>
       <c r="BQ10" s="1"/>
     </row>
-    <row r="11" spans="1:74" ht="21.95" customHeight="1">
-      <c r="A11" s="91"/>
+    <row r="11" spans="1:74" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="82"/>
       <c r="B11" s="26" t="s">
         <v>29</v>
       </c>
@@ -2511,8 +2516,8 @@
       <c r="BP11" s="10"/>
       <c r="BQ11" s="1"/>
     </row>
-    <row r="12" spans="1:74" ht="21.95" customHeight="1">
-      <c r="A12" s="91"/>
+    <row r="12" spans="1:74" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="82"/>
       <c r="B12" s="26" t="s">
         <v>36</v>
       </c>
@@ -2573,8 +2578,8 @@
       <c r="BP12" s="10"/>
       <c r="BQ12" s="1"/>
     </row>
-    <row r="13" spans="1:74" ht="21.95" customHeight="1">
-      <c r="A13" s="91"/>
+    <row r="13" spans="1:74" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="82"/>
       <c r="B13" s="26" t="s">
         <v>36</v>
       </c>
@@ -2653,8 +2658,8 @@
       <c r="BQ13" s="1"/>
       <c r="BU13" s="12"/>
     </row>
-    <row r="14" spans="1:74" ht="21.95" customHeight="1">
-      <c r="A14" s="91"/>
+    <row r="14" spans="1:74" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="82"/>
       <c r="B14" s="27" t="s">
         <v>41</v>
       </c>
@@ -2712,8 +2717,8 @@
       <c r="BT14" s="13"/>
       <c r="BV14" s="1"/>
     </row>
-    <row r="15" spans="1:74" ht="21.95" customHeight="1">
-      <c r="A15" s="91"/>
+    <row r="15" spans="1:74" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="82"/>
       <c r="B15" s="27" t="s">
         <v>41</v>
       </c>
@@ -2770,8 +2775,8 @@
       <c r="BQ15" s="1"/>
       <c r="BU15" s="3"/>
     </row>
-    <row r="16" spans="1:74" ht="21.95" customHeight="1">
-      <c r="A16" s="91"/>
+    <row r="16" spans="1:74" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="82"/>
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -2827,8 +2832,8 @@
       <c r="BP16" s="10"/>
       <c r="BQ16" s="1"/>
     </row>
-    <row r="17" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A17" s="91"/>
+    <row r="17" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="82"/>
       <c r="B17" s="27" t="s">
         <v>46</v>
       </c>
@@ -2884,8 +2889,8 @@
       <c r="BP17" s="10"/>
       <c r="BQ17" s="1"/>
     </row>
-    <row r="18" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A18" s="91"/>
+    <row r="18" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="82"/>
       <c r="B18" s="27" t="s">
         <v>46</v>
       </c>
@@ -2941,8 +2946,8 @@
       <c r="BP18" s="10"/>
       <c r="BQ18" s="1"/>
     </row>
-    <row r="19" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A19" s="91"/>
+    <row r="19" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="82"/>
       <c r="B19" s="27" t="s">
         <v>46</v>
       </c>
@@ -2997,8 +3002,8 @@
       <c r="BP19" s="10"/>
       <c r="BQ19" s="1"/>
     </row>
-    <row r="20" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A20" s="91"/>
+    <row r="20" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="82"/>
       <c r="B20" s="27" t="s">
         <v>50</v>
       </c>
@@ -3057,8 +3062,8 @@
       <c r="BP20" s="10"/>
       <c r="BQ20" s="1"/>
     </row>
-    <row r="21" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A21" s="91"/>
+    <row r="21" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="82"/>
       <c r="B21" s="27" t="s">
         <v>50</v>
       </c>
@@ -3077,8 +3082,8 @@
       <c r="BP21" s="14"/>
       <c r="BQ21" s="1"/>
     </row>
-    <row r="22" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A22" s="91"/>
+    <row r="22" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="82"/>
       <c r="B22" s="27" t="s">
         <v>53</v>
       </c>
@@ -3096,8 +3101,8 @@
       <c r="BP22" s="14"/>
       <c r="BQ22" s="1"/>
     </row>
-    <row r="23" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A23" s="91"/>
+    <row r="23" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="82"/>
       <c r="B23" s="27" t="s">
         <v>53</v>
       </c>
@@ -3115,8 +3120,8 @@
       <c r="BP23" s="14"/>
       <c r="BQ23" s="1"/>
     </row>
-    <row r="24" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A24" s="91"/>
+    <row r="24" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="82"/>
       <c r="B24" s="27" t="s">
         <v>46</v>
       </c>
@@ -3135,8 +3140,8 @@
       <c r="BP24" s="14"/>
       <c r="BQ24" s="1"/>
     </row>
-    <row r="25" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A25" s="91"/>
+    <row r="25" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="82"/>
       <c r="B25" s="27" t="s">
         <v>46</v>
       </c>
@@ -3156,8 +3161,8 @@
       <c r="BP25" s="14"/>
       <c r="BQ25" s="1"/>
     </row>
-    <row r="26" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A26" s="91"/>
+    <row r="26" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="82"/>
       <c r="B26" s="27" t="s">
         <v>46</v>
       </c>
@@ -3177,8 +3182,8 @@
       <c r="BP26" s="14"/>
       <c r="BQ26" s="1"/>
     </row>
-    <row r="27" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A27" s="91"/>
+    <row r="27" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="82"/>
       <c r="B27" s="27" t="s">
         <v>59</v>
       </c>
@@ -3197,8 +3202,8 @@
       <c r="BP27" s="14"/>
       <c r="BQ27" s="1"/>
     </row>
-    <row r="28" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A28" s="91"/>
+    <row r="28" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="82"/>
       <c r="B28" s="27" t="s">
         <v>59</v>
       </c>
@@ -3276,8 +3281,8 @@
       <c r="BP28" s="15"/>
       <c r="BQ28" s="1"/>
     </row>
-    <row r="29" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A29" s="91"/>
+    <row r="29" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="82"/>
       <c r="B29" s="27" t="s">
         <v>59</v>
       </c>
@@ -3295,8 +3300,8 @@
       <c r="BP29" s="14"/>
       <c r="BQ29" s="1"/>
     </row>
-    <row r="30" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A30" s="91"/>
+    <row r="30" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="82"/>
       <c r="B30" s="29" t="s">
         <v>63</v>
       </c>
@@ -3316,8 +3321,8 @@
       <c r="BP30" s="14"/>
       <c r="BQ30" s="1"/>
     </row>
-    <row r="31" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A31" s="91"/>
+    <row r="31" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="82"/>
       <c r="B31" s="27" t="s">
         <v>46</v>
       </c>
@@ -3337,8 +3342,8 @@
       <c r="BP31" s="14"/>
       <c r="BQ31" s="1"/>
     </row>
-    <row r="32" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A32" s="91"/>
+    <row r="32" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="82"/>
       <c r="B32" s="27" t="s">
         <v>46</v>
       </c>
@@ -3351,14 +3356,14 @@
       <c r="E32" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="AL32" s="97"/>
-      <c r="AM32" s="97"/>
-      <c r="AN32" s="97"/>
+      <c r="AL32" s="73"/>
+      <c r="AM32" s="73"/>
+      <c r="AN32" s="73"/>
       <c r="BP32" s="14"/>
       <c r="BQ32" s="1"/>
     </row>
-    <row r="33" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A33" s="91"/>
+    <row r="33" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="82"/>
       <c r="B33" s="27" t="s">
         <v>68</v>
       </c>
@@ -3436,8 +3441,8 @@
       <c r="BP33" s="15"/>
       <c r="BQ33" s="1"/>
     </row>
-    <row r="34" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A34" s="91"/>
+    <row r="34" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="82"/>
       <c r="B34" s="27" t="s">
         <v>68</v>
       </c>
@@ -3455,8 +3460,8 @@
       <c r="BP34" s="14"/>
       <c r="BQ34" s="1"/>
     </row>
-    <row r="35" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A35" s="91"/>
+    <row r="35" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="82"/>
       <c r="B35" s="27" t="s">
         <v>46</v>
       </c>
@@ -3534,8 +3539,8 @@
       <c r="BP35" s="62"/>
       <c r="BQ35" s="1"/>
     </row>
-    <row r="36" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A36" s="92"/>
+    <row r="36" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="83"/>
       <c r="B36" s="28" t="s">
         <v>46</v>
       </c>
@@ -3613,8 +3618,8 @@
       <c r="BP36" s="8"/>
       <c r="BQ36" s="1"/>
     </row>
-    <row r="37" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A37" s="93" t="s">
+    <row r="37" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="84" t="s">
         <v>73</v>
       </c>
       <c r="B37" s="29" t="s">
@@ -3694,8 +3699,8 @@
       <c r="BP37" s="15"/>
       <c r="BQ37" s="1"/>
     </row>
-    <row r="38" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A38" s="93"/>
+    <row r="38" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="84"/>
       <c r="B38" s="27" t="s">
         <v>74</v>
       </c>
@@ -3708,15 +3713,15 @@
       <c r="E38" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="AS38" s="97"/>
-      <c r="AT38" s="97"/>
-      <c r="AU38" s="97"/>
-      <c r="AV38" s="97"/>
+      <c r="AS38" s="73"/>
+      <c r="AT38" s="73"/>
+      <c r="AU38" s="73"/>
+      <c r="AV38" s="73"/>
       <c r="BP38" s="14"/>
       <c r="BQ38" s="1"/>
     </row>
-    <row r="39" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A39" s="93"/>
+    <row r="39" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="84"/>
       <c r="B39" s="27" t="s">
         <v>46</v>
       </c>
@@ -3729,15 +3734,15 @@
       <c r="E39" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="AP39" s="97"/>
-      <c r="AQ39" s="97"/>
-      <c r="AR39" s="97"/>
-      <c r="AS39" s="97"/>
+      <c r="AP39" s="73"/>
+      <c r="AQ39" s="73"/>
+      <c r="AR39" s="73"/>
+      <c r="AS39" s="73"/>
       <c r="BP39" s="14"/>
       <c r="BQ39" s="1"/>
     </row>
-    <row r="40" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A40" s="94"/>
+    <row r="40" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="85"/>
       <c r="B40" s="28" t="s">
         <v>79</v>
       </c>
@@ -3793,10 +3798,10 @@
       <c r="AT40" s="7"/>
       <c r="AU40" s="7"/>
       <c r="AV40" s="7"/>
-      <c r="AW40" s="101"/>
-      <c r="AX40" s="101"/>
-      <c r="AY40" s="101"/>
-      <c r="AZ40" s="101"/>
+      <c r="AW40" s="77"/>
+      <c r="AX40" s="77"/>
+      <c r="AY40" s="77"/>
+      <c r="AZ40" s="77"/>
       <c r="BA40" s="7"/>
       <c r="BB40" s="7"/>
       <c r="BC40" s="7"/>
@@ -3815,7 +3820,7 @@
       <c r="BP40" s="8"/>
       <c r="BQ40" s="1"/>
     </row>
-    <row r="41" spans="1:69" ht="21.95" customHeight="1">
+    <row r="41" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="21" t="s">
         <v>81</v>
       </c>
@@ -3878,12 +3883,12 @@
       <c r="AX41" s="18"/>
       <c r="AY41" s="18"/>
       <c r="AZ41" s="18"/>
-      <c r="BA41" s="99"/>
-      <c r="BB41" s="99"/>
-      <c r="BC41" s="99"/>
-      <c r="BD41" s="99"/>
-      <c r="BE41" s="99"/>
-      <c r="BF41" s="99"/>
+      <c r="BA41" s="75"/>
+      <c r="BB41" s="75"/>
+      <c r="BC41" s="75"/>
+      <c r="BD41" s="75"/>
+      <c r="BE41" s="75"/>
+      <c r="BF41" s="75"/>
       <c r="BG41" s="18"/>
       <c r="BH41" s="18"/>
       <c r="BI41" s="18"/>
@@ -3896,8 +3901,8 @@
       <c r="BP41" s="19"/>
       <c r="BQ41" s="1"/>
     </row>
-    <row r="42" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A42" s="95" t="s">
+    <row r="42" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="86" t="s">
         <v>84</v>
       </c>
       <c r="B42" s="29" t="s">
@@ -3965,20 +3970,20 @@
       <c r="BD42" s="3"/>
       <c r="BE42" s="3"/>
       <c r="BF42" s="3"/>
-      <c r="BG42" s="100"/>
-      <c r="BH42" s="100"/>
-      <c r="BI42" s="100"/>
-      <c r="BJ42" s="100"/>
-      <c r="BK42" s="100"/>
-      <c r="BL42" s="100"/>
-      <c r="BM42" s="100"/>
+      <c r="BG42" s="76"/>
+      <c r="BH42" s="76"/>
+      <c r="BI42" s="76"/>
+      <c r="BJ42" s="76"/>
+      <c r="BK42" s="76"/>
+      <c r="BL42" s="76"/>
+      <c r="BM42" s="76"/>
       <c r="BN42" s="3"/>
       <c r="BO42" s="3"/>
       <c r="BP42" s="15"/>
       <c r="BQ42" s="1"/>
     </row>
-    <row r="43" spans="1:69" ht="21.95" customHeight="1">
-      <c r="A43" s="96"/>
+    <row r="43" spans="1:69" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="87"/>
       <c r="B43" s="31" t="s">
         <v>84</v>
       </c>
@@ -4051,12 +4056,12 @@
       <c r="BK43" s="16"/>
       <c r="BL43" s="16"/>
       <c r="BM43" s="16"/>
-      <c r="BN43" s="102"/>
-      <c r="BO43" s="102"/>
-      <c r="BP43" s="103"/>
+      <c r="BN43" s="78"/>
+      <c r="BO43" s="78"/>
+      <c r="BP43" s="79"/>
       <c r="BQ43" s="1"/>
     </row>
-    <row r="44" spans="1:69">
+    <row r="44" spans="1:69" x14ac:dyDescent="0.2">
       <c r="A44" s="22"/>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -4127,12 +4132,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A36"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="F5:L5"/>
-    <mergeCell ref="B4:B5"/>
     <mergeCell ref="T5:Z5"/>
     <mergeCell ref="AO5:AU5"/>
     <mergeCell ref="A1:BP3"/>
@@ -4149,6 +4148,12 @@
     <mergeCell ref="AV5:BB5"/>
     <mergeCell ref="M5:S5"/>
     <mergeCell ref="BC5:BI5"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A36"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="B4:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
